--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-participation-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
